--- a/reports/intelligence/SENTINEL_INTELLIGENCE_REPORT.xlsx
+++ b/reports/intelligence/SENTINEL_INTELLIGENCE_REPORT.xlsx
@@ -459,12 +459,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.9.5.161</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v0.9.5.161_report_architecture</t>
+          <t>v0.9.5.162_history_integrity_report_hygiene</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11616,7 +11616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11637,75 +11637,80 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>decision_state_hash</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>case_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>server</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>evidence_fingerprint</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>classification_fingerprint</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>decision_hash</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>failure_class</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>failure_domain</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>review_action</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>resolution_readiness</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>resolution_strategy</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>root_cause_confidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>recommendation_score</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>review_confidence</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>required_evidence_coverage</t>
         </is>
@@ -11727,67 +11732,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>S551-R8</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>551</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5acceabcf643472eaef64d76ed11f85a582b31b7c6d539d242196672393029f9</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>8868cf8a3e6bebf240a83f5f44f7a798972c6c9b480cac9f0300311e775a546c</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>86fe604128ceb41e297236ca2c4dc57a419f4c6d5a222b797c6ffa2d7165eaae</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>REVIEW_MISSING_IDENTITY</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>WAITING_FOR_EVIDENCE</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>COLLECT_IDENTITY_EVIDENCE</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.8055</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.7486</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>0.6636</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -11807,67 +11813,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>S551-R23</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>551</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>9a2f1519bb3f9bcb3b2261cf6bf23b271bf5ff316aae6726943ae66f04d6cbba</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>3399af3bb97193e4d2682dba3627b1a253b0454044eca7fd35469f26fa54dc5e</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>795d559a292ccfe15c88adc33797399e455aaf999d603d53b41106269defb8c4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>observed_text_confirmed</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>evidence_against_expected</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>REVIEW_EVIDENCE_CONFLICT</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>READY_FOR_MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>MANUAL_EVIDENCE_ADJUDICATION</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.9585</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0.8729</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>0.9244</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11887,67 +11894,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>S551-R36</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>551</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>36</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>7203c523cf562dbbe1b4c5d6aae34af90a14b928cd15279e0e662ceb6100b7fe</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3b1342916ffdb941301914c7a90bdb8d85908389c69513360f76806303cff7b9</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>df0b9d39ab3768c6a48a831102fd73b54cb01f1ea240ea17b921b45b25ed39b4</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>REVIEW_MISSING_IDENTITY</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>WAITING_FOR_EVIDENCE</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>COLLECT_IDENTITY_EVIDENCE</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.8055</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0.7486</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0.6636</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -11967,67 +11975,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>S551-R42</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>551</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>42</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>011cbc60117e26595a99151cb2c338794d62121e8cd0ca2bfef8c735ff95de0f</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>02886785576ae20c1ab9c1cdd1e1779dd1699a357ba75fd3f4440d7daf232f42</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0300280b5491d1f005e20ea8e5574ad071aadf99f8c066733464d9253761d5ae</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>observed_text_confirmed</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>evidence_against_expected</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>REVIEW_EVIDENCE_CONFLICT</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>READY_FOR_MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>MANUAL_EVIDENCE_ADJUDICATION</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.9585</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>0.8729</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>0.893</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12047,67 +12056,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>S551-R43</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>551</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>43</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>d26f5d1c0b875fa73b86618bfa122fdf215c9d3a5609e6400b3ccf3c3962e2f8</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>d391bb0656e00029eae637775e65cdf41ef026fa56b5183962f09319a70a51f0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>93cfcada77adc7e35561219184bc1cf51a69c5f21d29d65fbf41417e07db4e37</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>observed_text_confirmed</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>evidence_against_expected</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>REVIEW_EVIDENCE_CONFLICT</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>READY_FOR_MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>MANUAL_EVIDENCE_ADJUDICATION</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.9585</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>0.8729</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>0.9</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12127,67 +12137,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>S551-R2</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>551</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>cbd14c7ec754dc019e448baf2d632eb945a70458ec1bec4d58318e7ff2af958e</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>98d5b33da66b0750469edfb671f2badf086342a7a343e08bf430536654e5ee17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>8fd04f368adb55e0017cd3e2609d48116e0a36ec3aa962791e860e030a55378f</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>policy_nonlocal_script_display</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>script_display_policy</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>REVIEW_SCRIPT_POLICY</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>POLICY_DECISION_REQUIRED</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.9375</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0.8396</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>0.842</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -12207,67 +12218,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>S551-R11</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>551</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>11</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>9ae6970f9e4482bedd9611bea4ec4f58d1d5b3d50b8296521064daee0e6a7358</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>d14fed49c6ecd517484cee3a85bad0a66371ea44b15b4328f387cfeefd45f20a</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>a2ef5428927563d80a1e069b4c6e1fec19bd355cde79d1fbccbcf7aaceb2e6ed</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>REVIEW_VOTE_SELECTION</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.9435</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.8811</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>0.8478</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -12287,67 +12299,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>S551-R19</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>551</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>19</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>81d63d7d83a0edc0fa665fe3b18ec49b5515893e85dba56e71b14851c6427815</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>be802cf4271573574c801192467192dd1c13f8c962b2c6606004823258cbbfaf</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>52ce9ff2d8459b248f547508563f4671a6ca99d570d1e5d29920a30492aea056</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>mixed_local_and_nonlocal_blocker</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>local_glyph_plus_script_display</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>REVIEW_MIXED_SCRIPT</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>POLICY_DECISION_REQUIRED</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0.9405</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>0.8524</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>0.8511</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -12367,67 +12380,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>S551-R20</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>551</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>20</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>192ccaa6a36d82fda93eb630b61f542c16a85604b953938c2bfa3d56126488b2</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>9a18f97821e28b909fc7ecd842d4d3106a8a89da7ae37fc357ec6fd90d53640e</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>171829300429c6563c1cca01c4229d068aadb0a1815215cce090a4916b81e694</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>local_glyph_solvable</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>latin_local_glyph</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>REVIEW_LOCAL_GLYPH</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>TARGETED_LOCAL_GLYPH_REOCR</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>0.9495</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.9186</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>0.8961</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -12447,67 +12461,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>S551-R39</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>551</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>39</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>a1924c3ce2899c2605b9b84c2af60961355eb4b6fb1df9048234931ae0a41e47</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1017166f0b90b927a0e86e6c9a32f7abb0c27ae3a85afd5ffe418337e99d7910</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0ef8cbc12becd20ea80baa755721d4feb6b2606ceac15ec4eae505d9de9a2373</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>crop_geometry_problem</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>crop_anchor_or_field_bleed</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>REVIEW_CROP_GEOMETRY</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>RECROP_AND_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.9555</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.9201</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>0.8232</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -12527,67 +12542,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>S551-R41</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>551</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>41</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>bdbc3cab4a35fbbf30c7076c72e9718064a47c053ad0c3df43b675e00c6e5450</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>c0c9a367d94cfeadeb1242e79fb1db81013c2bd4ed33d0d0bfee8f7e5642dcf4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>aac8ae098c0465ab9c9c57d45f890335c0812c4d62afa673d680895bc7329372</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>crop_geometry_problem</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>crop_anchor_or_field_bleed</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>REVIEW_CROP_GEOMETRY</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>RECROP_AND_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.9555</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0.9201</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>0.8455</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -12607,67 +12623,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>S551-R45</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>551</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>45</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>65d17618a0cdce3be811f121a5edffc558ca1e1419903cc9652908c45045d17c</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>c6182801e53fabc3b81388f666a8d513064fbf2c938082c6e1fb38d1c88e286c</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>17b8cadfbbca8bec465ebe1130d0c90777a65811440a16db20131e912136e27a</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>crop_geometry_problem</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>crop_anchor_or_field_bleed</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>REVIEW_CROP_GEOMETRY</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>RECROP_AND_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0.9555</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>0.9201</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>0.8455</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -12687,67 +12704,68 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>S551-R48</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>551</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>48</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>e9af5cb87696aa1db78a0d7767366136ac06f7665d88e06bea9b677c8d5513c3</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>dba156898a83335d9f1091b861101761b49f213ac5382ba3a0976fc4f9a8d594</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0c56cc5231a75e9a5969efef5df2a36c52e7aed1f3dc37b40f251a6bef3ef8df</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>REVIEW_VOTE_SELECTION</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0.9435</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0.8811</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>0.8195</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -12767,67 +12785,1258 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>S551-R50</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>551</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>50</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>5e6695a610a743d97e155fca6a6b4cae8aaf59af225b43bc713e3101889e7cbd</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>5b82c5730a355562faae480ff413578e9f5553f2e73a22372e4e80d1a33fb948</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>d0f6b08a685e04c7f03f1843935c5d77cf30758eae9f8d0073d51bd8f34b9aa1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>REVIEW_VOTE_SELECTION</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>0.9435</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>0.8811</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>0.8234</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S551-R8</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5acceabcf643472eaef64d76ed11f85a582b31b7c6d539d242196672393029f9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8868cf8a3e6bebf240a83f5f44f7a798972c6c9b480cac9f0300311e775a546c</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>86fe604128ceb41e297236ca2c4dc57a419f4c6d5a222b797c6ffa2d7165eaae</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>REVIEW_MISSING_IDENTITY</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>COLLECT_IDENTITY_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7486</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>S551-R23</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>9a2f1519bb3f9bcb3b2261cf6bf23b271bf5ff316aae6726943ae66f04d6cbba</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3399af3bb97193e4d2682dba3627b1a253b0454044eca7fd35469f26fa54dc5e</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>795d559a292ccfe15c88adc33797399e455aaf999d603d53b41106269defb8c4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>observed_text_confirmed</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>evidence_against_expected</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>REVIEW_EVIDENCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>READY_FOR_MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MANUAL_EVIDENCE_ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9244</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>S551-R36</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="n">
+        <v>36</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>7203c523cf562dbbe1b4c5d6aae34af90a14b928cd15279e0e662ceb6100b7fe</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3b1342916ffdb941301914c7a90bdb8d85908389c69513360f76806303cff7b9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>df0b9d39ab3768c6a48a831102fd73b54cb01f1ea240ea17b921b45b25ed39b4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>REVIEW_MISSING_IDENTITY</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>COLLECT_IDENTITY_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7486</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>S551-R42</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="n">
+        <v>42</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>011cbc60117e26595a99151cb2c338794d62121e8cd0ca2bfef8c735ff95de0f</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>02886785576ae20c1ab9c1cdd1e1779dd1699a357ba75fd3f4440d7daf232f42</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0300280b5491d1f005e20ea8e5574ad071aadf99f8c066733464d9253761d5ae</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>observed_text_confirmed</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>evidence_against_expected</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>REVIEW_EVIDENCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>READY_FOR_MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MANUAL_EVIDENCE_ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>S551-R43</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>551</v>
+      </c>
+      <c r="G20" t="n">
+        <v>43</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>d26f5d1c0b875fa73b86618bfa122fdf215c9d3a5609e6400b3ccf3c3962e2f8</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>d391bb0656e00029eae637775e65cdf41ef026fa56b5183962f09319a70a51f0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>93cfcada77adc7e35561219184bc1cf51a69c5f21d29d65fbf41417e07db4e37</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>observed_text_confirmed</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>evidence_against_expected</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>REVIEW_EVIDENCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>READY_FOR_MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MANUAL_EVIDENCE_ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>S551-R2</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>551</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>cbd14c7ec754dc019e448baf2d632eb945a70458ec1bec4d58318e7ff2af958e</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>98d5b33da66b0750469edfb671f2badf086342a7a343e08bf430536654e5ee17</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>8fd04f368adb55e0017cd3e2609d48116e0a36ec3aa962791e860e030a55378f</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>policy_nonlocal_script_display</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>script_display_policy</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>REVIEW_SCRIPT_POLICY</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>POLICY_DECISION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8396</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>S551-R11</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>551</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>9ae6970f9e4482bedd9611bea4ec4f58d1d5b3d50b8296521064daee0e6a7358</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>d14fed49c6ecd517484cee3a85bad0a66371ea44b15b4328f387cfeefd45f20a</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>a2ef5428927563d80a1e069b4c6e1fec19bd355cde79d1fbccbcf7aaceb2e6ed</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>REVIEW_VOTE_SELECTION</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.8478</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S551-R19</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>551</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>81d63d7d83a0edc0fa665fe3b18ec49b5515893e85dba56e71b14851c6427815</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>be802cf4271573574c801192467192dd1c13f8c962b2c6606004823258cbbfaf</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>52ce9ff2d8459b248f547508563f4671a6ca99d570d1e5d29920a30492aea056</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>mixed_local_and_nonlocal_blocker</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>local_glyph_plus_script_display</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>REVIEW_MIXED_SCRIPT</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>POLICY_DECISION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.8524</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.8511</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>S551-R20</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>551</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>192ccaa6a36d82fda93eb630b61f542c16a85604b953938c2bfa3d56126488b2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9a18f97821e28b909fc7ecd842d4d3106a8a89da7ae37fc357ec6fd90d53640e</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>171829300429c6563c1cca01c4229d068aadb0a1815215cce090a4916b81e694</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>local_glyph_solvable</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>latin_local_glyph</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>REVIEW_LOCAL_GLYPH</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TARGETED_LOCAL_GLYPH_REOCR</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9495</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.9186</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>S551-R39</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>551</v>
+      </c>
+      <c r="G25" t="n">
+        <v>39</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>a1924c3ce2899c2605b9b84c2af60961355eb4b6fb1df9048234931ae0a41e47</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1017166f0b90b927a0e86e6c9a32f7abb0c27ae3a85afd5ffe418337e99d7910</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0ef8cbc12becd20ea80baa755721d4feb6b2606ceac15ec4eae505d9de9a2373</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>crop_geometry_problem</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>crop_anchor_or_field_bleed</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>REVIEW_CROP_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>RECROP_AND_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S551-R41</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>551</v>
+      </c>
+      <c r="G26" t="n">
+        <v>41</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>bdbc3cab4a35fbbf30c7076c72e9718064a47c053ad0c3df43b675e00c6e5450</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>c0c9a367d94cfeadeb1242e79fb1db81013c2bd4ed33d0d0bfee8f7e5642dcf4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>aac8ae098c0465ab9c9c57d45f890335c0812c4d62afa673d680895bc7329372</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>crop_geometry_problem</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>crop_anchor_or_field_bleed</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>REVIEW_CROP_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>RECROP_AND_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S551-R45</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>551</v>
+      </c>
+      <c r="G27" t="n">
+        <v>45</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>65d17618a0cdce3be811f121a5edffc558ca1e1419903cc9652908c45045d17c</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>c6182801e53fabc3b81388f666a8d513064fbf2c938082c6e1fb38d1c88e286c</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>17b8cadfbbca8bec465ebe1130d0c90777a65811440a16db20131e912136e27a</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>crop_geometry_problem</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>crop_anchor_or_field_bleed</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>REVIEW_CROP_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>RECROP_AND_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>S551-R48</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>551</v>
+      </c>
+      <c r="G28" t="n">
+        <v>48</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>e9af5cb87696aa1db78a0d7767366136ac06f7665d88e06bea9b677c8d5513c3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>dba156898a83335d9f1091b861101761b49f213ac5382ba3a0976fc4f9a8d594</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0c56cc5231a75e9a5969efef5df2a36c52e7aed1f3dc37b40f251a6bef3ef8df</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>REVIEW_VOTE_SELECTION</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S551-R50</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>551</v>
+      </c>
+      <c r="G29" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5e6695a610a743d97e155fca6a6b4cae8aaf59af225b43bc713e3101889e7cbd</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5b82c5730a355562faae480ff413578e9f5553f2e73a22372e4e80d1a33fb948</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>d0f6b08a685e04c7f03f1843935c5d77cf30758eae9f8d0073d51bd8f34b9aa1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>REVIEW_VOTE_SELECTION</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.8234</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -12842,7 +14051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12863,85 +14072,90 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>decision_state_hash</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>case_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>server</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>evidence_fingerprint</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>classification_fingerprint</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>decision_hash</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>failure_class</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>failure_domain</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>review_action</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>resolution_readiness</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>resolution_strategy</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>root_cause_confidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>recommendation_score</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>review_confidence</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>required_evidence_coverage</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>drift_attribution</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
@@ -12963,75 +14177,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>S551-R8</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>551</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5acceabcf643472eaef64d76ed11f85a582b31b7c6d539d242196672393029f9</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>8868cf8a3e6bebf240a83f5f44f7a798972c6c9b480cac9f0300311e775a546c</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>86fe604128ceb41e297236ca2c4dc57a419f4c6d5a222b797c6ffa2d7165eaae</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>REVIEW_MISSING_IDENTITY</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>WAITING_FOR_EVIDENCE</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>COLLECT_IDENTITY_EVIDENCE</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.8055</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.7486</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>0.6636</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>0.5</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13053,75 +14268,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>S551-R23</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>551</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>9a2f1519bb3f9bcb3b2261cf6bf23b271bf5ff316aae6726943ae66f04d6cbba</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>3399af3bb97193e4d2682dba3627b1a253b0454044eca7fd35469f26fa54dc5e</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>795d559a292ccfe15c88adc33797399e455aaf999d603d53b41106269defb8c4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>observed_text_confirmed</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>evidence_against_expected</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>REVIEW_EVIDENCE_CONFLICT</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>READY_FOR_MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>MANUAL_EVIDENCE_ADJUDICATION</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.9585</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0.8729</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>0.9244</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13143,75 +14359,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>S551-R36</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>551</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>36</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>7203c523cf562dbbe1b4c5d6aae34af90a14b928cd15279e0e662ceb6100b7fe</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3b1342916ffdb941301914c7a90bdb8d85908389c69513360f76806303cff7b9</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>df0b9d39ab3768c6a48a831102fd73b54cb01f1ea240ea17b921b45b25ed39b4</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>REVIEW_MISSING_IDENTITY</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>WAITING_FOR_EVIDENCE</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>COLLECT_IDENTITY_EVIDENCE</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.8055</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0.7486</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0.6636</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0.5</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13233,75 +14450,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>S551-R42</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>551</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>42</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>011cbc60117e26595a99151cb2c338794d62121e8cd0ca2bfef8c735ff95de0f</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>02886785576ae20c1ab9c1cdd1e1779dd1699a357ba75fd3f4440d7daf232f42</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0300280b5491d1f005e20ea8e5574ad071aadf99f8c066733464d9253761d5ae</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>observed_text_confirmed</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>evidence_against_expected</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>REVIEW_EVIDENCE_CONFLICT</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>READY_FOR_MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>MANUAL_EVIDENCE_ADJUDICATION</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.9585</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>0.8729</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>0.893</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13323,75 +14541,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>S551-R43</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>551</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>43</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>d26f5d1c0b875fa73b86618bfa122fdf215c9d3a5609e6400b3ccf3c3962e2f8</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>d391bb0656e00029eae637775e65cdf41ef026fa56b5183962f09319a70a51f0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>93cfcada77adc7e35561219184bc1cf51a69c5f21d29d65fbf41417e07db4e37</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>observed_text_confirmed</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>evidence_against_expected</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>REVIEW_EVIDENCE_CONFLICT</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>READY_FOR_MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>MANUAL_EVIDENCE_ADJUDICATION</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.9585</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>0.8729</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>0.9</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13413,75 +14632,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>S551-R2</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>551</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>cbd14c7ec754dc019e448baf2d632eb945a70458ec1bec4d58318e7ff2af958e</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>98d5b33da66b0750469edfb671f2badf086342a7a343e08bf430536654e5ee17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>8fd04f368adb55e0017cd3e2609d48116e0a36ec3aa962791e860e030a55378f</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>policy_nonlocal_script_display</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>script_display_policy</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>REVIEW_SCRIPT_POLICY</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>POLICY_DECISION_REQUIRED</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.9375</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0.8396</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>0.842</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.75</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13503,75 +14723,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>S551-R11</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>551</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>11</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>9ae6970f9e4482bedd9611bea4ec4f58d1d5b3d50b8296521064daee0e6a7358</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>d14fed49c6ecd517484cee3a85bad0a66371ea44b15b4328f387cfeefd45f20a</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>a2ef5428927563d80a1e069b4c6e1fec19bd355cde79d1fbccbcf7aaceb2e6ed</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>REVIEW_VOTE_SELECTION</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.9435</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.8811</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>0.8478</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>0.5</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13593,75 +14814,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>S551-R19</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>551</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>19</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>81d63d7d83a0edc0fa665fe3b18ec49b5515893e85dba56e71b14851c6427815</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>be802cf4271573574c801192467192dd1c13f8c962b2c6606004823258cbbfaf</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>52ce9ff2d8459b248f547508563f4671a6ca99d570d1e5d29920a30492aea056</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>mixed_local_and_nonlocal_blocker</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>local_glyph_plus_script_display</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>REVIEW_MIXED_SCRIPT</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>POLICY_DECISION_REQUIRED</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0.9405</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>0.8524</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>0.8511</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>0.75</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13683,75 +14905,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>S551-R20</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>551</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>20</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>192ccaa6a36d82fda93eb630b61f542c16a85604b953938c2bfa3d56126488b2</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>9a18f97821e28b909fc7ecd842d4d3106a8a89da7ae37fc357ec6fd90d53640e</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>171829300429c6563c1cca01c4229d068aadb0a1815215cce090a4916b81e694</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>local_glyph_solvable</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>latin_local_glyph</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>REVIEW_LOCAL_GLYPH</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>TARGETED_LOCAL_GLYPH_REOCR</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>0.9495</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.9186</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>0.8961</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>0.75</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13773,75 +14996,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>S551-R39</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>551</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>39</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>a1924c3ce2899c2605b9b84c2af60961355eb4b6fb1df9048234931ae0a41e47</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1017166f0b90b927a0e86e6c9a32f7abb0c27ae3a85afd5ffe418337e99d7910</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0ef8cbc12becd20ea80baa755721d4feb6b2606ceac15ec4eae505d9de9a2373</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>crop_geometry_problem</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>crop_anchor_or_field_bleed</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>REVIEW_CROP_GEOMETRY</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>RECROP_AND_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.9555</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.9201</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>0.8232</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>0.4</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13863,75 +15087,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>S551-R41</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>551</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>41</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>bdbc3cab4a35fbbf30c7076c72e9718064a47c053ad0c3df43b675e00c6e5450</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>c0c9a367d94cfeadeb1242e79fb1db81013c2bd4ed33d0d0bfee8f7e5642dcf4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>aac8ae098c0465ab9c9c57d45f890335c0812c4d62afa673d680895bc7329372</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>crop_geometry_problem</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>crop_anchor_or_field_bleed</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>REVIEW_CROP_GEOMETRY</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>RECROP_AND_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.9555</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0.9201</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>0.8455</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.4</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13953,75 +15178,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>S551-R45</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>551</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>45</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>65d17618a0cdce3be811f121a5edffc558ca1e1419903cc9652908c45045d17c</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>c6182801e53fabc3b81388f666a8d513064fbf2c938082c6e1fb38d1c88e286c</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>17b8cadfbbca8bec465ebe1130d0c90777a65811440a16db20131e912136e27a</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>crop_geometry_problem</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>crop_anchor_or_field_bleed</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>REVIEW_CROP_GEOMETRY</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>RECROP_AND_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0.9555</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>0.9201</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>0.8455</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>0.4</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -14043,75 +15269,76 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>S551-R48</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>551</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>48</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>e9af5cb87696aa1db78a0d7767366136ac06f7665d88e06bea9b677c8d5513c3</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>dba156898a83335d9f1091b861101761b49f213ac5382ba3a0976fc4f9a8d594</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0c56cc5231a75e9a5969efef5df2a36c52e7aed1f3dc37b40f251a6bef3ef8df</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>REVIEW_VOTE_SELECTION</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0.9435</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0.8811</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>0.8195</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>0.5</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -14133,75 +15360,1406 @@
           <t>0.9.5.159</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>S551-R50</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>551</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>50</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>5e6695a610a743d97e155fca6a6b4cae8aaf59af225b43bc713e3101889e7cbd</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>5b82c5730a355562faae480ff413578e9f5553f2e73a22372e4e80d1a33fb948</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>d0f6b08a685e04c7f03f1843935c5d77cf30758eae9f8d0073d51bd8f34b9aa1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>vote_warning_gate_review</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>vote_selection_policy</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>REVIEW_VOTE_SELECTION</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>READY_FOR_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>0.9435</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>0.8811</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>0.8234</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>0.5</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S551-R8</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5acceabcf643472eaef64d76ed11f85a582b31b7c6d539d242196672393029f9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8868cf8a3e6bebf240a83f5f44f7a798972c6c9b480cac9f0300311e775a546c</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>86fe604128ceb41e297236ca2c4dc57a419f4c6d5a222b797c6ffa2d7165eaae</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>REVIEW_MISSING_IDENTITY</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>COLLECT_IDENTITY_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7486</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>S551-R23</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>9a2f1519bb3f9bcb3b2261cf6bf23b271bf5ff316aae6726943ae66f04d6cbba</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3399af3bb97193e4d2682dba3627b1a253b0454044eca7fd35469f26fa54dc5e</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>795d559a292ccfe15c88adc33797399e455aaf999d603d53b41106269defb8c4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>observed_text_confirmed</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>evidence_against_expected</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>REVIEW_EVIDENCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>READY_FOR_MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MANUAL_EVIDENCE_ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9244</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>S551-R36</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="n">
+        <v>36</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>7203c523cf562dbbe1b4c5d6aae34af90a14b928cd15279e0e662ceb6100b7fe</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3b1342916ffdb941301914c7a90bdb8d85908389c69513360f76806303cff7b9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>df0b9d39ab3768c6a48a831102fd73b54cb01f1ea240ea17b921b45b25ed39b4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>REVIEW_MISSING_IDENTITY</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>COLLECT_IDENTITY_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7486</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>S551-R42</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="n">
+        <v>42</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>011cbc60117e26595a99151cb2c338794d62121e8cd0ca2bfef8c735ff95de0f</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>02886785576ae20c1ab9c1cdd1e1779dd1699a357ba75fd3f4440d7daf232f42</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0300280b5491d1f005e20ea8e5574ad071aadf99f8c066733464d9253761d5ae</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>observed_text_confirmed</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>evidence_against_expected</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>REVIEW_EVIDENCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>READY_FOR_MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MANUAL_EVIDENCE_ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>S551-R43</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>551</v>
+      </c>
+      <c r="G20" t="n">
+        <v>43</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>d26f5d1c0b875fa73b86618bfa122fdf215c9d3a5609e6400b3ccf3c3962e2f8</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>d391bb0656e00029eae637775e65cdf41ef026fa56b5183962f09319a70a51f0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>93cfcada77adc7e35561219184bc1cf51a69c5f21d29d65fbf41417e07db4e37</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>observed_text_confirmed</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>evidence_against_expected</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>REVIEW_EVIDENCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>READY_FOR_MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MANUAL_EVIDENCE_ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>S551-R2</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>551</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>cbd14c7ec754dc019e448baf2d632eb945a70458ec1bec4d58318e7ff2af958e</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>98d5b33da66b0750469edfb671f2badf086342a7a343e08bf430536654e5ee17</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>8fd04f368adb55e0017cd3e2609d48116e0a36ec3aa962791e860e030a55378f</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>policy_nonlocal_script_display</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>script_display_policy</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>REVIEW_SCRIPT_POLICY</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>POLICY_DECISION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8396</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>S551-R11</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>551</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>9ae6970f9e4482bedd9611bea4ec4f58d1d5b3d50b8296521064daee0e6a7358</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>d14fed49c6ecd517484cee3a85bad0a66371ea44b15b4328f387cfeefd45f20a</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>a2ef5428927563d80a1e069b4c6e1fec19bd355cde79d1fbccbcf7aaceb2e6ed</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>REVIEW_VOTE_SELECTION</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.8478</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S551-R19</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>551</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>81d63d7d83a0edc0fa665fe3b18ec49b5515893e85dba56e71b14851c6427815</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>be802cf4271573574c801192467192dd1c13f8c962b2c6606004823258cbbfaf</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>52ce9ff2d8459b248f547508563f4671a6ca99d570d1e5d29920a30492aea056</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>mixed_local_and_nonlocal_blocker</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>local_glyph_plus_script_display</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>REVIEW_MIXED_SCRIPT</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>POLICY_DECISION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MANUAL_SCRIPT_POLICY_REVIEW</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.8524</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.8511</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>S551-R20</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>551</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>192ccaa6a36d82fda93eb630b61f542c16a85604b953938c2bfa3d56126488b2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9a18f97821e28b909fc7ecd842d4d3106a8a89da7ae37fc357ec6fd90d53640e</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>171829300429c6563c1cca01c4229d068aadb0a1815215cce090a4916b81e694</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>local_glyph_solvable</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>latin_local_glyph</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>REVIEW_LOCAL_GLYPH</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TARGETED_LOCAL_GLYPH_REOCR</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9495</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.9186</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>S551-R39</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>551</v>
+      </c>
+      <c r="G25" t="n">
+        <v>39</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>a1924c3ce2899c2605b9b84c2af60961355eb4b6fb1df9048234931ae0a41e47</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1017166f0b90b927a0e86e6c9a32f7abb0c27ae3a85afd5ffe418337e99d7910</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0ef8cbc12becd20ea80baa755721d4feb6b2606ceac15ec4eae505d9de9a2373</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>crop_geometry_problem</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>crop_anchor_or_field_bleed</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>REVIEW_CROP_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>RECROP_AND_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S551-R41</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>551</v>
+      </c>
+      <c r="G26" t="n">
+        <v>41</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>bdbc3cab4a35fbbf30c7076c72e9718064a47c053ad0c3df43b675e00c6e5450</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>c0c9a367d94cfeadeb1242e79fb1db81013c2bd4ed33d0d0bfee8f7e5642dcf4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>aac8ae098c0465ab9c9c57d45f890335c0812c4d62afa673d680895bc7329372</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>crop_geometry_problem</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>crop_anchor_or_field_bleed</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>REVIEW_CROP_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>RECROP_AND_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S551-R45</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>551</v>
+      </c>
+      <c r="G27" t="n">
+        <v>45</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>65d17618a0cdce3be811f121a5edffc558ca1e1419903cc9652908c45045d17c</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>c6182801e53fabc3b81388f666a8d513064fbf2c938082c6e1fb38d1c88e286c</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>17b8cadfbbca8bec465ebe1130d0c90777a65811440a16db20131e912136e27a</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>crop_geometry_problem</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>crop_anchor_or_field_bleed</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>REVIEW_CROP_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>RECROP_AND_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>S551-R48</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>551</v>
+      </c>
+      <c r="G28" t="n">
+        <v>48</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>e9af5cb87696aa1db78a0d7767366136ac06f7665d88e06bea9b677c8d5513c3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>dba156898a83335d9f1091b861101761b49f213ac5382ba3a0976fc4f9a8d594</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0c56cc5231a75e9a5969efef5df2a36c52e7aed1f3dc37b40f251a6bef3ef8df</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>REVIEW_VOTE_SELECTION</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:40:43+00:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1328b1d21b6535a0dd3f52d17c717fe59f096f257ea636671e1371d1af29ed87</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S551-R50</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>551</v>
+      </c>
+      <c r="G29" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5e6695a610a743d97e155fca6a6b4cae8aaf59af225b43bc713e3101889e7cbd</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5b82c5730a355562faae480ff413578e9f5553f2e73a22372e4e80d1a33fb948</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>d0f6b08a685e04c7f03f1843935c5d77cf30758eae9f8d0073d51bd8f34b9aa1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vote_warning_gate_review</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>vote_selection_policy</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>REVIEW_VOTE_SELECTION</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>READY_FOR_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>REPLAY_VOTE_SELECTION_WITH_TARGETED_REOCR</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.8234</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -14326,7 +16884,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -14336,7 +16894,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -14408,7 +16966,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -14418,7 +16976,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -14490,7 +17048,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -14500,7 +17058,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -14572,7 +17130,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -14582,7 +17140,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -14654,7 +17212,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -14664,7 +17222,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -14736,7 +17294,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -14746,7 +17304,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -14818,7 +17376,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14828,7 +17386,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -14900,7 +17458,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14910,7 +17468,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -14982,7 +17540,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14992,7 +17550,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -15064,7 +17622,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15074,7 +17632,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -15146,7 +17704,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15156,7 +17714,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -15228,7 +17786,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15238,7 +17796,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -15310,7 +17868,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15320,7 +17878,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -15392,7 +17950,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9.5.159-37bdd778188a</t>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15402,7 +17960,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.9.5.159</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="F15" t="b">
